--- a/artfynd/A 25880-2026 artfynd.xlsx
+++ b/artfynd/A 25880-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91373351</v>
+        <v>6884843</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillberget, Vb</t>
+          <t>Stenbäcken - Vallnäs, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702791.9384083858</v>
+        <v>702805</v>
       </c>
       <c r="R2" t="n">
-        <v>7164889.158033131</v>
+        <v>7164805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Henrik Sporrong, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91373353</v>
+        <v>6906174</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillberget, Vb</t>
+          <t>Stenbäcken - Vallnäs, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702793.7103903184</v>
+        <v>702811</v>
       </c>
       <c r="R3" t="n">
-        <v>7164979.005258244</v>
+        <v>7164860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,21 +853,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -912,16 +872,11 @@
         <v>91373354</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702783.5323408272</v>
+        <v>702784</v>
       </c>
       <c r="R4" t="n">
-        <v>7165002.051198448</v>
+        <v>7165002</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +937,9 @@
           <t>2021-03-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91373352</v>
+        <v>91373350</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702793.7103903184</v>
+        <v>702792</v>
       </c>
       <c r="R5" t="n">
-        <v>7164979.005258244</v>
+        <v>7164889</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1034,9 @@
           <t>2021-03-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91373350</v>
+        <v>91373353</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>702791.9384083858</v>
+        <v>702794</v>
       </c>
       <c r="R6" t="n">
-        <v>7164889.158033131</v>
+        <v>7164979</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1136,9 @@
           <t>2021-03-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,6 +1167,210 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91373351</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>702792</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7164889</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91373352</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>702794</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7164979</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
